--- a/samples/历史销量导入-示例.xlsx
+++ b/samples/历史销量导入-示例.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -535,13 +535,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>帆布鞋</v>
+        <v>夏季T恤</v>
       </c>
       <c r="B13" s="1">
-        <v>46255</v>
+        <v>46271</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -549,10 +549,10 @@
         <v>帆布鞋</v>
       </c>
       <c r="B14" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -560,10 +560,10 @@
         <v>帆布鞋</v>
       </c>
       <c r="B15" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -571,10 +571,10 @@
         <v>帆布鞋</v>
       </c>
       <c r="B16" s="1">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -582,32 +582,32 @@
         <v>帆布鞋</v>
       </c>
       <c r="B17" s="1">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>保温杯</v>
+        <v>帆布鞋</v>
       </c>
       <c r="B18" s="1">
-        <v>46257</v>
+        <v>46270</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>保温杯</v>
+        <v>帆布鞋</v>
       </c>
       <c r="B19" s="1">
-        <v>46261</v>
+        <v>46271</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="20">
@@ -615,10 +615,10 @@
         <v>保温杯</v>
       </c>
       <c r="B20" s="1">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -626,43 +626,43 @@
         <v>保温杯</v>
       </c>
       <c r="B21" s="1">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="C21">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>运动袜</v>
+        <v>保温杯</v>
       </c>
       <c r="B22" s="1">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="C22">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>运动袜</v>
+        <v>保温杯</v>
       </c>
       <c r="B23" s="1">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="C23">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>运动袜</v>
+        <v>保温杯</v>
       </c>
       <c r="B24" s="1">
-        <v>46263</v>
-      </c>
-      <c r="C24" t="str">
-        <v>1,200</v>
+        <v>46271</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -670,10 +670,10 @@
         <v>运动袜</v>
       </c>
       <c r="B25" s="1">
-        <v>46266</v>
+        <v>46256</v>
       </c>
       <c r="C25">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -681,15 +681,48 @@
         <v>运动袜</v>
       </c>
       <c r="B26" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C26">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>运动袜</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C27" t="str">
+        <v>1,200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>运动袜</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C28">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>运动袜</v>
+      </c>
+      <c r="B29" s="1">
         <v>46270</v>
       </c>
-      <c r="C26">
+      <c r="C29">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
   </ignoredErrors>
 </worksheet>
 </file>